--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
         <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>93.333333333333</v>
+        <v>120</v>
       </c>
       <c r="L16" s="15">
-        <v>20.833333333333</v>
+        <v>17.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.705882352941</v>
+        <v>-17.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.763713080168</v>
+        <v>-87.258687258687</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.333333333333</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>-37.777777777777</v>
+        <v>-26</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.707317073170</v>
+        <v>-26</v>
       </c>
       <c r="M17" s="15">
-        <v>-26.315789473684</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="N17" s="15">
-        <v>-74.774774774774</v>
+        <v>-71.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>11.111111111111</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>9.090909090909</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.454545454545</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.731707317073</v>
+        <v>-64.444444444444</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.549295774647</v>
+        <v>-90.062111801242</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>43.478260869565</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J19" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K19" s="15">
-        <v>41.935483870967</v>
+        <v>27.027027027027</v>
       </c>
       <c r="L19" s="15">
-        <v>2.325581395348</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="M19" s="15">
-        <v>41.935483870967</v>
+        <v>23.684210526315</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.111111111111</v>
+        <v>-52.525252525252</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.153846153846</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-53.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.857142857142</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F21" s="17">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>19.512195121951</v>
+        <v>3.529411764705</v>
       </c>
       <c r="I21" s="17">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="J21" s="17">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="K21" s="18">
-        <v>12.5</v>
+        <v>11.450381679389</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.103448275862</v>
+        <v>-12.574850299401</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.699386503067</v>
+        <v>-21.925133689839</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.222056631892</v>
+        <v>-80.507343124165</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
         <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="M23" s="15">
-        <v>61.538461538461</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>23</v>
+      </c>
+      <c r="D24" s="14">
         <v>24</v>
       </c>
-      <c r="D24" s="14">
-        <v>14</v>
-      </c>
       <c r="E24" s="15">
-        <v>71.428571428571</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.111111111111</v>
+        <v>-6.593406593406</v>
       </c>
       <c r="I24" s="14">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="J24" s="14">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="K24" s="15">
-        <v>7.964601769911</v>
+        <v>5.109489051094</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.230215827338</v>
+        <v>-10.559006211180</v>
       </c>
       <c r="M24" s="15">
-        <v>25.773195876288</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>57.142857142857</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>12.195121951219</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I25" s="14">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K25" s="15">
-        <v>21.568627450980</v>
+        <v>25</v>
       </c>
       <c r="L25" s="15">
-        <v>8.771929824561</v>
+        <v>19.047619047619</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-40.909090909090</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>-32</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="I26" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.413793103448</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>-37.5</v>
+        <v>-27.710843373494</v>
       </c>
       <c r="M26" s="15">
-        <v>-41.558441558441</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1412,7 +1412,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-83.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,29 +1466,29 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
@@ -1497,39 +1497,39 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-96</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-69.230769230769</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>120</v>
+        <v>105.555555555556</v>
       </c>
       <c r="L16" s="15">
-        <v>17.857142857142</v>
+        <v>15.625</v>
       </c>
       <c r="M16" s="15">
-        <v>-17.5</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.258687258687</v>
+        <v>-88.178913738019</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>10.714285714285</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I17" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="L17" s="15">
-        <v>-26</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M17" s="15">
-        <v>-13.953488372093</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-71.538461538461</v>
+        <v>-70.422535211267</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.882352941176</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.434782608695</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.444444444444</v>
+        <v>-67.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.062111801242</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
         <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>8.333333333333</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J19" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K19" s="15">
-        <v>27.027027027027</v>
+        <v>27.906976744186</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.081632653061</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="M19" s="15">
-        <v>23.684210526315</v>
+        <v>10</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.525252525252</v>
+        <v>-47.619047619047</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
@@ -1119,19 +1119,19 @@
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="L20" s="15">
-        <v>-53.333333333333</v>
+        <v>-56.25</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.823529411764</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>5.263157894736</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>3.529411764705</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I21" s="17">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="K21" s="18">
-        <v>11.450381679389</v>
+        <v>7.792207792207</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.574850299401</v>
+        <v>-12.631578947368</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.925133689839</v>
+        <v>-26.222222222222</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.507343124165</v>
+        <v>-80.607476635514</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>125</v>
+        <v>87.5</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>62.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L23" s="15">
-        <v>-25.714285714285</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M23" s="15">
-        <v>85.714285714285</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.166666666666</v>
+        <v>23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.593406593406</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="J24" s="14">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="K24" s="15">
-        <v>5.109489051094</v>
+        <v>6.962025316455</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.559006211180</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M24" s="15">
-        <v>23.076923076923</v>
+        <v>36.290322580645</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>15.384615384615</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="I25" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J25" s="14">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K25" s="15">
-        <v>25</v>
+        <v>15.277777777777</v>
       </c>
       <c r="L25" s="15">
-        <v>19.047619047619</v>
+        <v>20.289855072463</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.122448979591</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J26" s="14">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.285714285714</v>
+        <v>-20.224719101123</v>
       </c>
       <c r="L26" s="15">
-        <v>-27.710843373494</v>
+        <v>-23.655913978494</v>
       </c>
       <c r="M26" s="15">
-        <v>-34.782608695652</v>
+        <v>-33.644859813084</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-57.142857142857</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-55.555555555555</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,14 +1466,14 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1497,24 +1497,24 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.592592592592</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1538,42 +1538,42 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.304347826087</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>2</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,33 +873,33 @@
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,16 +914,16 @@
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-66.666666666666</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>4</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
         <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>105.555555555556</v>
+        <v>94.736842105263</v>
       </c>
       <c r="L16" s="15">
-        <v>15.625</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M16" s="15">
-        <v>-13.953488372093</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.178913738019</v>
+        <v>-89.664804469273</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
         <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.407407407407</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15">
-        <v>-25</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="L17" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="M17" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="N17" s="15">
-        <v>-70.422535211267</v>
+        <v>-69.375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-71.428571428571</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.058823529411</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.769230769230</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.272727272727</v>
+        <v>-70.491803278688</v>
       </c>
       <c r="N18" s="15">
-        <v>-90</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.703703703703</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K19" s="15">
-        <v>27.906976744186</v>
+        <v>20.408163265306</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.779661016949</v>
+        <v>-16.901408450704</v>
       </c>
       <c r="M19" s="15">
-        <v>10</v>
+        <v>9.259259259259</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.619047619047</v>
+        <v>-50.833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>-30</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L20" s="15">
-        <v>-56.25</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-63.157894736842</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.857142857142</v>
+        <v>-90.566037735849</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.739130434782</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.111111111111</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="I21" s="17">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="J21" s="17">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="K21" s="18">
-        <v>7.792207792207</v>
+        <v>2.272727272727</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.631578947368</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.222222222222</v>
+        <v>-29.961089494163</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.607476635514</v>
+        <v>-81.308411214953</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>300</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>87.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K23" s="15">
-        <v>55.555555555555</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.222222222222</v>
+        <v>-32.5</v>
       </c>
       <c r="M23" s="15">
-        <v>55.555555555555</v>
+        <v>12.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>23.809523809523</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.333333333333</v>
+        <v>2.325581395348</v>
       </c>
       <c r="I24" s="14">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J24" s="14">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>6.962025316455</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.142857142857</v>
+        <v>-14.746543778801</v>
       </c>
       <c r="M24" s="15">
-        <v>36.290322580645</v>
+        <v>41.221374045801</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
         <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-10.869565217391</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="K25" s="15">
-        <v>15.277777777777</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>20.289855072463</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.105263157894</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.354838709677</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J26" s="14">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.224719101123</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.655913978494</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M26" s="15">
-        <v>-33.644859813084</v>
+        <v>-34.959349593495</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-54.545454545454</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.333333333333</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,18 +1538,18 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,24 +873,24 @@
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L14" s="15">
+        <v>100</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -905,22 +905,22 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -931,262 +931,262 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>140</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>94.736842105263</v>
+        <v>105</v>
       </c>
       <c r="L16" s="15">
-        <v>2.777777777777</v>
+        <v>2.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.916666666666</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.664804469273</v>
+        <v>-89.540816326530</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>11.538461538461</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K17" s="15">
-        <v>-20.967741935483</v>
+        <v>-18.309859154929</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.757575757575</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M17" s="15">
-        <v>-25.757575757575</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.375</v>
+        <v>-68.131868131868</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F18" s="14">
+        <v>11</v>
+      </c>
+      <c r="G18" s="14">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>10</v>
-      </c>
-      <c r="G18" s="14">
-        <v>19</v>
-      </c>
       <c r="H18" s="15">
-        <v>-47.368421052631</v>
+        <v>-45</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.714285714285</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="L18" s="15">
-        <v>-40</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.491803278688</v>
+        <v>-67.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-91</v>
+        <v>-89.639639639639</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="14">
         <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.793103448275</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K19" s="15">
-        <v>20.408163265306</v>
+        <v>18.965517241379</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.901408450704</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M19" s="15">
-        <v>9.259259259259</v>
+        <v>11.290322580645</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.833333333333</v>
+        <v>-47.328244274809</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
+        <v>500</v>
+      </c>
+      <c r="F20" s="14">
+        <v>10</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I20" s="14">
+        <v>16</v>
+      </c>
+      <c r="J20" s="14">
+        <v>14</v>
+      </c>
+      <c r="K20" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="L20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>5</v>
-      </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="I20" s="14">
-        <v>10</v>
-      </c>
-      <c r="J20" s="14">
-        <v>13</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-23.076923076923</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-37.5</v>
-      </c>
       <c r="M20" s="15">
-        <v>-52.380952380952</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.566037735849</v>
+        <v>-86.554621848739</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.363636363636</v>
+        <v>32</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.304347826087</v>
+        <v>-1.123595505617</v>
       </c>
       <c r="I21" s="17">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="J21" s="17">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="K21" s="18">
-        <v>2.272727272727</v>
+        <v>6.467661691542</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.918918918918</v>
+        <v>-13.709677419354</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.961089494163</v>
+        <v>-26.206896551724</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.308411214953</v>
+        <v>-79.962546816479</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1213,48 +1213,48 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>17.391304347826</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L23" s="15">
-        <v>-32.5</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>12.5</v>
+        <v>19.230769230769</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-40.740740740740</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H24" s="15">
-        <v>2.325581395348</v>
+        <v>-8.602150537634</v>
       </c>
       <c r="I24" s="14">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K24" s="15">
         <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.746543778801</v>
+        <v>-14.522821576763</v>
       </c>
       <c r="M24" s="15">
-        <v>41.221374045801</v>
+        <v>42.068965517241</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-77.777777777777</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F25" s="14">
         <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.565217391304</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="I25" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K25" s="15">
-        <v>-3.333333333333</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.333333333333</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
         <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.809523809523</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="I26" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J26" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.191919191919</v>
+        <v>-21.100917431192</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.528301886792</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-34.959349593495</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1397,69 +1397,69 @@
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="E28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-61.538461538461</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>-71.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.594594594594</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.548387096774</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>98</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2442</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1349</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1706</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>867</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>744</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>7277</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -885,21 +885,21 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -926,258 +926,258 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>140</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>105</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>2.5</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.641509433962</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.540816326530</v>
+        <v>-89.719626168224</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="14">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="15">
+        <v>500</v>
+      </c>
+      <c r="F17" s="14">
+        <v>33</v>
+      </c>
+      <c r="G17" s="14">
         <v>23</v>
       </c>
-      <c r="C17" s="14">
-        <v>8</v>
-      </c>
-      <c r="D17" s="14">
-        <v>9</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="H17" s="15">
+        <v>43.478260869565</v>
+      </c>
+      <c r="I17" s="14">
+        <v>72</v>
+      </c>
+      <c r="J17" s="14">
+        <v>73</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-1.369863013698</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="M17" s="15">
         <v>-11.111111111111</v>
       </c>
-      <c r="F17" s="14">
-        <v>29</v>
-      </c>
-      <c r="G17" s="14">
-        <v>26</v>
-      </c>
-      <c r="H17" s="15">
-        <v>11.538461538461</v>
-      </c>
-      <c r="I17" s="14">
-        <v>58</v>
-      </c>
-      <c r="J17" s="14">
-        <v>71</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-18.309859154929</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-23.684210526315</v>
-      </c>
-      <c r="M17" s="15">
-        <v>-23.684210526315</v>
-      </c>
       <c r="N17" s="15">
-        <v>-68.131868131868</v>
+        <v>-64.179104477611</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-45</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.806451612903</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.303030303030</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.639639639639</v>
+        <v>-88.796680497925</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.407407407407</v>
+        <v>17.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J19" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>18.965517241379</v>
+        <v>24.615384615384</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.538461538461</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>11.290322580645</v>
+        <v>15.714285714285</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.328244274809</v>
+        <v>-44.897959183673</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I20" s="14">
+        <v>19</v>
+      </c>
+      <c r="J20" s="14">
         <v>16</v>
       </c>
-      <c r="J20" s="14">
-        <v>14</v>
-      </c>
       <c r="K20" s="15">
-        <v>14.285714285714</v>
+        <v>18.75</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="M20" s="15">
-        <v>-27.272727272727</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.554621848739</v>
+        <v>-85.496183206106</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>32</v>
+        <v>89.473684210526</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
         <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.123595505617</v>
+        <v>14.606741573033</v>
       </c>
       <c r="I21" s="17">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="J21" s="17">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K21" s="18">
-        <v>6.467661691542</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.709677419354</v>
+        <v>-8.424908424908</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.206896551724</v>
+        <v>-22.600619195046</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.962546816479</v>
+        <v>-78.668941979522</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1186,16 +1186,16 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>10.714285714285</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.111111111111</v>
+        <v>-24</v>
       </c>
       <c r="M23" s="15">
-        <v>19.230769230769</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.761904761904</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.602150537634</v>
+        <v>-19</v>
       </c>
       <c r="I24" s="14">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="J24" s="14">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>-5.485232067510</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.522821576763</v>
+        <v>-16.728624535316</v>
       </c>
       <c r="M24" s="15">
-        <v>42.068965517241</v>
+        <v>38.271604938271</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.428571428571</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H25" s="15">
-        <v>-30.188679245283</v>
+        <v>-54.098360655737</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J25" s="14">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.769230769230</v>
+        <v>-14.876033057851</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.921568627450</v>
+        <v>-7.207207207207</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
         <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-40</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.607843137254</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="I26" s="14">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="J26" s="14">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.100917431192</v>
+        <v>-10.924369747899</v>
       </c>
       <c r="L26" s="15">
-        <v>-28.333333333333</v>
+        <v>-19.083969465648</v>
       </c>
       <c r="M26" s="15">
-        <v>-35.820895522388</v>
+        <v>-27.397260273972</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1415,133 +1415,133 @@
         <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>29</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>-28.571428571428</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-53.846153846153</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-71.428571428571</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.238095238095</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L30" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M30" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="N30" s="15">
-        <v>-94.285714285714</v>
+        <v>-89.743589743589</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>3</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>98</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2442</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1349</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1706</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>867</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>744</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>7277</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -882,92 +882,92 @@
         <v>100</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
+        <v>7</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-68.75</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>22.222222222222</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="14">
         <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>83.333333333333</v>
+        <v>62.962962962963</v>
       </c>
       <c r="L16" s="15">
-        <v>-2.222222222222</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="M16" s="15">
-        <v>-24.137931034482</v>
+        <v>-32.307692307692</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.719626168224</v>
+        <v>-90.537634408602</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>500</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
         <v>33</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>43.478260869565</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.369863013698</v>
+        <v>-1.25</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.285714285714</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="M17" s="15">
-        <v>-11.111111111111</v>
+        <v>-9.195402298850</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.179104477611</v>
+        <v>-63.255813953488</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.857142857142</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.857142857142</v>
+        <v>-22.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-67.368421052631</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.796680497925</v>
+        <v>-87.984496124031</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>85.714285714285</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>17.857142857142</v>
+        <v>-3.125</v>
       </c>
       <c r="I19" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>24.615384615384</v>
+        <v>16</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.954545454545</v>
+        <v>-8.421052631578</v>
       </c>
       <c r="M19" s="15">
-        <v>15.714285714285</v>
+        <v>16</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.897959183673</v>
+        <v>-46.296296296296</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>71.428571428571</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>18.75</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L20" s="15">
-        <v>18.75</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.923076923076</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.496183206106</v>
+        <v>-84.246575342465</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>89.473684210526</v>
+        <v>-24</v>
       </c>
       <c r="F21" s="17">
         <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>14.606741573033</v>
+        <v>12.087912087912</v>
       </c>
       <c r="I21" s="17">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="J21" s="17">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="K21" s="18">
-        <v>13.636363636363</v>
+        <v>11.428571428571</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.424908424908</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.600619195046</v>
+        <v>-24.166666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.668941979522</v>
+        <v>-78.554595443833</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,16 +1201,16 @@
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>6</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
         <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>26.666666666666</v>
+        <v>21.875</v>
       </c>
       <c r="L23" s="15">
-        <v>-24</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>46.153846153846</v>
+        <v>21.875</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.935483870967</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-19</v>
+        <v>-28.971962616822</v>
       </c>
       <c r="I24" s="14">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="J24" s="14">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.485232067510</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.728624535316</v>
+        <v>-19.407894736842</v>
       </c>
       <c r="M24" s="15">
-        <v>38.271604938271</v>
+        <v>36.871508379888</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
         <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-70.588235294117</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F25" s="14">
         <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.098360655737</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="I25" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J25" s="14">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.876033057851</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.207207207207</v>
+        <v>-7.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.122448979591</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.924369747899</v>
+        <v>-12.977099236641</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.083969465648</v>
+        <v>-18.571428571428</v>
       </c>
       <c r="M26" s="15">
-        <v>-27.397260273972</v>
+        <v>-31.325301204819</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
         <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-57.142857142857</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.304347826087</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.743589743589</v>
+        <v>-91.111111111111</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -873,10 +873,10 @@
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>100</v>
@@ -885,89 +885,89 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N15" s="15">
-        <v>-56.25</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>62.962962962963</v>
+        <v>60</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.725490196078</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.307692307692</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.537634408602</v>
+        <v>-90.283400809716</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>37.5</v>
+        <v>9.375</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J17" s="14">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.25</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.130434782608</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M17" s="15">
-        <v>-9.195402298850</v>
+        <v>-5.376344086021</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.255813953488</v>
+        <v>-64.227642276422</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.216216216216</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.5</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.368421052631</v>
+        <v>-68.316831683168</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.984496124031</v>
+        <v>-88.405797101449</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
         <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.125</v>
+        <v>-6.25</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K19" s="15">
-        <v>16</v>
+        <v>12.345679012345</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.421052631578</v>
+        <v>-9</v>
       </c>
       <c r="M19" s="15">
-        <v>16</v>
+        <v>15.189873417721</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.296296296296</v>
+        <v>-48.295454545454</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>27.777777777777</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>35.294117647058</v>
+        <v>47.368421052631</v>
       </c>
       <c r="M20" s="15">
-        <v>-17.857142857142</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.246575342465</v>
+        <v>-82.278481012658</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,122 +1139,122 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-24</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>12.087912087912</v>
+        <v>13.265306122449</v>
       </c>
       <c r="I21" s="17">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="J21" s="17">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>11.428571428571</v>
+        <v>8.759124087591</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.302325581395</v>
+        <v>-6.583072100313</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.166666666666</v>
+        <v>-22.193211488250</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.554595443833</v>
+        <v>-78.405797101449</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.428571428571</v>
+        <v>-18.75</v>
       </c>
       <c r="I23" s="14">
+        <v>43</v>
+      </c>
+      <c r="J23" s="14">
         <v>39</v>
       </c>
-      <c r="J23" s="14">
-        <v>32</v>
-      </c>
       <c r="K23" s="15">
-        <v>21.875</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L23" s="15">
-        <v>-29.090909090909</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="M23" s="15">
-        <v>21.875</v>
+        <v>19.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.857142857142</v>
+        <v>-55.932203389830</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.971962616822</v>
+        <v>-38.848920863309</v>
       </c>
       <c r="I24" s="14">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="J24" s="14">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.547169811320</v>
+        <v>-16.358024691358</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.407894736842</v>
+        <v>-14.511041009463</v>
       </c>
       <c r="M24" s="15">
-        <v>36.871508379888</v>
+        <v>36.180904522613</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E25" s="15">
-        <v>-52.941176470588</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-57.575757575757</v>
+        <v>-55.952380952380</v>
       </c>
       <c r="I25" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J25" s="14">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="K25" s="15">
-        <v>-19.565217391304</v>
+        <v>-28.735632183908</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.5</v>
+        <v>-3.125</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>4.761904761904</v>
+        <v>21.951219512195</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J26" s="14">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.977099236641</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.571428571428</v>
+        <v>-12.751677852349</v>
       </c>
       <c r="M26" s="15">
-        <v>-31.325301204819</v>
+        <v>-28.176795580110</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-50</v>
-      </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-46.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.111111111111</v>
+        <v>30</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,7 +1473,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1494,13 +1494,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="15">
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,7 +1514,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1535,13 +1535,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.111111111111</v>
+        <v>-92.452830188679</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1575,14 +1575,14 @@
       <c r="K31" s="15">
         <v>150</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>98</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
-        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -885,30 +885,30 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.433962264150</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.428571428571</v>
+        <v>-35.526315789473</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.283400809716</v>
+        <v>-90.806754221388</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>8</v>
       </c>
-      <c r="D17" s="14">
-        <v>14</v>
-      </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>9.375</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I17" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J17" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.382978723404</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="M17" s="15">
-        <v>-5.376344086021</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.227642276422</v>
+        <v>-65.441176470588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>27.272727272727</v>
+        <v>30</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-17.948717948717</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.809523809523</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="M18" s="15">
-        <v>-68.316831683168</v>
+        <v>-66.981132075471</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.405797101449</v>
+        <v>-88.524590163934</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.25</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I19" s="14">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>12.345679012345</v>
+        <v>11.494252873563</v>
       </c>
       <c r="L19" s="15">
-        <v>-9</v>
+        <v>-11.009174311926</v>
       </c>
       <c r="M19" s="15">
-        <v>15.189873417721</v>
+        <v>7.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.295454545454</v>
+        <v>-48.677248677248</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>4</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>33.333333333333</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>125</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I20" s="14">
         <v>28</v>
@@ -1125,13 +1125,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>47.368421052631</v>
+        <v>40</v>
       </c>
       <c r="M20" s="15">
-        <v>-3.448275862068</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.278481012658</v>
+        <v>-83.431952662721</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.689655172413</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H21" s="18">
-        <v>13.265306122449</v>
+        <v>1.063829787234</v>
       </c>
       <c r="I21" s="17">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>8.759124087591</v>
+        <v>6.440677966101</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.583072100313</v>
+        <v>-10.285714285714</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.193211488250</v>
+        <v>-23.970944309927</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.405797101449</v>
+        <v>-79.066666666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,31 +1189,31 @@
         <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>7</v>
-      </c>
       <c r="E23" s="15">
-        <v>-57.142857142857</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.75</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J23" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K23" s="15">
-        <v>10.256410256410</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L23" s="15">
-        <v>-27.118644067796</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="M23" s="15">
-        <v>19.444444444444</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-55.932203389830</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.848920863309</v>
+        <v>-34.751773049645</v>
       </c>
       <c r="I24" s="14">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="J24" s="14">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.358024691358</v>
+        <v>-14.697406340057</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.511041009463</v>
+        <v>-9.480122324159</v>
       </c>
       <c r="M24" s="15">
-        <v>36.180904522613</v>
+        <v>37.674418604651</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="F25" s="14">
         <v>36</v>
       </c>
-      <c r="E25" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F25" s="14">
-        <v>37</v>
-      </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" s="15">
-        <v>-55.952380952380</v>
+        <v>-56.626506024096</v>
       </c>
       <c r="I25" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="J25" s="14">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.735632183908</v>
+        <v>-28.342245989304</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.125</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>77.777777777777</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>21.951219512195</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I26" s="14">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.142857142857</v>
+        <v>-8.387096774193</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.751677852349</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.176795580110</v>
+        <v>-26.424870466321</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,16 +1473,16 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1494,13 +1494,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.548387096774</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1535,13 +1535,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M30" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.452830188679</v>
+        <v>-93.442622950819</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
@@ -1579,10 +1579,10 @@
         <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>98</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -885,15 +885,15 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,72 +902,72 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-52.631578947368</v>
+        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-46.666666666666</v>
+        <v>-68.75</v>
       </c>
       <c r="I16" s="14">
         <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>40</v>
+        <v>22.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.949152542372</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.526315789473</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.806754221388</v>
+        <v>-91.403508771929</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>3.225806451612</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I17" s="14">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.843137254901</v>
+        <v>-9.821428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.962962962963</v>
+        <v>-15.833333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>-4.081632653061</v>
+        <v>-10.619469026548</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.441176470588</v>
+        <v>-65.762711864406</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.634146341463</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.531914893617</v>
+        <v>-28</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.981132075471</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.524590163934</v>
+        <v>-89.057750759878</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.896551724137</v>
+        <v>-40.625</v>
       </c>
       <c r="I19" s="14">
+        <v>103</v>
+      </c>
+      <c r="J19" s="14">
         <v>97</v>
       </c>
-      <c r="J19" s="14">
-        <v>87</v>
-      </c>
       <c r="K19" s="15">
-        <v>11.494252873563</v>
+        <v>6.185567010309</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.009174311926</v>
+        <v>-11.206896551724</v>
       </c>
       <c r="M19" s="15">
-        <v>7.777777777777</v>
+        <v>-0.961538461538</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.677248677248</v>
+        <v>-51.415094339622</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>71.428571428571</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>20.833333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>40</v>
+        <v>31.818181818181</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.677419354838</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.431952662721</v>
+        <v>-83.428571428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>1.063829787234</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="I21" s="17">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="J21" s="17">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="K21" s="18">
-        <v>6.440677966101</v>
+        <v>1.851851851851</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.285714285714</v>
+        <v>-12.466843501326</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.970944309927</v>
+        <v>-27.631578947368</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.066666666666</v>
+        <v>-79.604449938195</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
         <v>50</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J23" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K23" s="15">
-        <v>9.523809523809</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-32.352941176470</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>21.052631578947</v>
+        <v>4.255319148936</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>8.695652173913</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G24" s="14">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.751773049645</v>
+        <v>-20</v>
       </c>
       <c r="I24" s="14">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="J24" s="14">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.697406340057</v>
+        <v>-12.201591511936</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.480122324159</v>
+        <v>-5.428571428571</v>
       </c>
       <c r="M24" s="15">
-        <v>37.674418604651</v>
+        <v>44.541484716157</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.626506024096</v>
+        <v>-38.961038961039</v>
       </c>
       <c r="I25" s="14">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="J25" s="14">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.342245989304</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>5.633802816901</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>13.043478260869</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J26" s="14">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.387096774193</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.476190476190</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="M26" s="15">
-        <v>-26.424870466321</v>
+        <v>-28.037383177570</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L28" s="15">
-        <v>27.272727272727</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.285714285714</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>2</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>-20</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.442622950819</v>
+        <v>-93.650793650793</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -885,89 +885,89 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N15" s="15">
-        <v>-56.521739130434</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-68.75</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>22.5</v>
+        <v>20.454545454545</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.672131147541</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.666666666666</v>
+        <v>-44.210526315789</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.403508771929</v>
+        <v>-91.196013289036</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-30</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" s="15">
-        <v>-30.769230769230</v>
+        <v>-35</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J17" s="14">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.821428571428</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.833333333333</v>
+        <v>-17.829457364341</v>
       </c>
       <c r="M17" s="15">
-        <v>-10.619469026548</v>
+        <v>-12.396694214876</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.762711864406</v>
+        <v>-66.875</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
         <v>9</v>
       </c>
-      <c r="G18" s="14">
-        <v>7</v>
-      </c>
       <c r="H18" s="15">
-        <v>28.571428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
         <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L18" s="15">
-        <v>-28</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.857142857142</v>
+        <v>-70</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.057750759878</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
-        <v>10</v>
-      </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-40.625</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I19" s="14">
+        <v>110</v>
+      </c>
+      <c r="J19" s="14">
         <v>103</v>
       </c>
-      <c r="J19" s="14">
-        <v>97</v>
-      </c>
       <c r="K19" s="15">
-        <v>6.185567010309</v>
+        <v>6.796116504854</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.206896551724</v>
+        <v>-5.982905982905</v>
       </c>
       <c r="M19" s="15">
-        <v>-0.961538461538</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.415094339622</v>
+        <v>-50.450450450450</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I20" s="14">
+        <v>30</v>
+      </c>
+      <c r="J20" s="14">
+        <v>26</v>
+      </c>
+      <c r="K20" s="15">
+        <v>15.384615384615</v>
+      </c>
+      <c r="L20" s="15">
         <v>25</v>
       </c>
-      <c r="I20" s="14">
-        <v>29</v>
-      </c>
-      <c r="J20" s="14">
-        <v>24</v>
-      </c>
-      <c r="K20" s="15">
-        <v>20.833333333333</v>
-      </c>
-      <c r="L20" s="15">
-        <v>31.818181818181</v>
-      </c>
       <c r="M20" s="15">
-        <v>-6.451612903225</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.428571428571</v>
+        <v>-83.870967741935</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.827586206896</v>
+        <v>-28</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
         <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.846153846153</v>
+        <v>-33.653846153846</v>
       </c>
       <c r="I21" s="17">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="J21" s="17">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="K21" s="18">
-        <v>1.851851851851</v>
+        <v>-0.573065902578</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.466843501326</v>
+        <v>-12.373737373737</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.631578947368</v>
+        <v>-30.321285140562</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.604449938195</v>
+        <v>-79.930595720069</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>3</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="I22" s="14">
+        <v>9</v>
+      </c>
+      <c r="J22" s="14">
         <v>6</v>
       </c>
-      <c r="J22" s="14">
-        <v>5</v>
-      </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M22" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
         <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J23" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K23" s="15">
-        <v>2.083333333333</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L23" s="15">
-        <v>-34.666666666666</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M23" s="15">
-        <v>4.255319148936</v>
+        <v>2.040816326530</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>13.333333333333</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F24" s="14">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G24" s="14">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15">
-        <v>-20</v>
+        <v>-27.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="J24" s="14">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.201591511936</v>
+        <v>-14.698795180722</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.428571428571</v>
+        <v>-6.100795755968</v>
       </c>
       <c r="M24" s="15">
-        <v>44.541484716157</v>
+        <v>42.168674698795</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>45.454545454545</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.961038961039</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="J25" s="14">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.242424242424</v>
+        <v>-26.576576576576</v>
       </c>
       <c r="L25" s="15">
-        <v>5.633802816901</v>
+        <v>8.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>83.333333333333</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>14.285714285714</v>
+        <v>48.717948717948</v>
       </c>
       <c r="I26" s="14">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.347826086956</v>
+        <v>1.176470588235</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.304347826087</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.037383177570</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>71.428571428571</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>13</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>10</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>233.333333333333</v>
+        <v>550</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
         <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.764705882352</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L28" s="15">
-        <v>15.384615384615</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-63.636363636363</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.594594594594</v>
+        <v>-95.061728395061</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-20</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.650793650793</v>
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -882,10 +882,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,28 +902,28 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-58.333333333333</v>
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.941176470588</v>
+        <v>-55</v>
       </c>
       <c r="I16" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K16" s="15">
-        <v>20.454545454545</v>
+        <v>16</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.461538461538</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.210526315789</v>
+        <v>-42</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.196013289036</v>
+        <v>-90.822784810126</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>-35</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="14">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J17" s="14">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.666666666666</v>
+        <v>-11.811023622047</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.829457364341</v>
+        <v>-19.424460431654</v>
       </c>
       <c r="M17" s="15">
-        <v>-12.396694214876</v>
+        <v>-14.503816793893</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.875</v>
+        <v>-67.058823529411</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.739130434782</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.075471698113</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M18" s="15">
-        <v>-70</v>
+        <v>-70.3125</v>
       </c>
       <c r="N18" s="15">
-        <v>-90</v>
+        <v>-90.026246719160</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.428571428571</v>
+        <v>-28.125</v>
       </c>
       <c r="I19" s="14">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J19" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>6.796116504854</v>
+        <v>3.539823008849</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.982905982905</v>
+        <v>-2.5</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.508771929824</v>
+        <v>-4.098360655737</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.450450450450</v>
+        <v>-49.785407725321</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M20" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.870967741935</v>
+        <v>-83.589743589743</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-28</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.653846153846</v>
+        <v>-36.792452830188</v>
       </c>
       <c r="I21" s="17">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="J21" s="17">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.573065902578</v>
+        <v>-2.894736842105</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.373737373737</v>
+        <v>-11.510791366906</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.321285140562</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.930595720069</v>
+        <v>-79.758639605046</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L22" s="15">
         <v>80</v>
@@ -1230,28 +1230,28 @@
         <v>-60</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-57.142857142857</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I23" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J23" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.660377358490</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.897435897435</v>
+        <v>-40.229885057471</v>
       </c>
       <c r="M23" s="15">
-        <v>2.040816326530</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.105263157894</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F24" s="14">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G24" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.333333333333</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="J24" s="14">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.698795180722</v>
+        <v>-15.090090090090</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.100795755968</v>
+        <v>-5.985037406483</v>
       </c>
       <c r="M24" s="15">
-        <v>42.168674698795</v>
+        <v>38.602941176470</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.833333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.285714285714</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="I25" s="14">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J25" s="14">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.576576576576</v>
+        <v>-26.582278481012</v>
       </c>
       <c r="L25" s="15">
-        <v>8.666666666666</v>
+        <v>10.126582278481</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>111.111111111111</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>48.717948717948</v>
+        <v>15.909090909090</v>
       </c>
       <c r="I26" s="14">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J26" s="14">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="K26" s="15">
-        <v>1.176470588235</v>
+        <v>-1.630434782608</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.340206185567</v>
+        <v>-14.218009478673</v>
       </c>
       <c r="M26" s="15">
-        <v>-24.561403508771</v>
+        <v>-27.309236947791</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>62.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>30</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>11.764705882352</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>35.714285714285</v>
+        <v>31.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M29" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.061728395061</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.939393939393</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
         <v>200</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -920,13 +920,13 @@
         <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.333333333333</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-55</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>16</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.142857142857</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-42</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.822784810126</v>
+        <v>-90.963855421686</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.272727272727</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J17" s="14">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.811023622047</v>
+        <v>-19.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-19.424460431654</v>
+        <v>-17.123287671232</v>
       </c>
       <c r="M17" s="15">
-        <v>-14.503816793893</v>
+        <v>-14.788732394366</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.058823529411</v>
+        <v>-67.119565217391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.148936170212</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-29.629629629629</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.3125</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.026246719160</v>
+        <v>-89.393939393939</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
         <v>7</v>
       </c>
-      <c r="D19" s="14">
-        <v>10</v>
-      </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.125</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="I19" s="14">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>3.539823008849</v>
+        <v>7.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.5</v>
+        <v>3.2</v>
       </c>
       <c r="M19" s="15">
-        <v>-4.098360655737</v>
+        <v>0.78125</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.785407725321</v>
+        <v>-48.809523809523</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
         <v>6</v>
       </c>
-      <c r="E20" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F20" s="14">
-        <v>4</v>
-      </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>3.030303030303</v>
       </c>
       <c r="L20" s="15">
-        <v>28</v>
+        <v>25.925925925925</v>
       </c>
       <c r="M20" s="15">
-        <v>-13.513513513513</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.589743589743</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.483870967741</v>
+        <v>-37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H21" s="18">
-        <v>-36.792452830188</v>
+        <v>-36.8</v>
       </c>
       <c r="I21" s="17">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J21" s="17">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.894736842105</v>
+        <v>-5.238095238095</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.510791366906</v>
+        <v>-10.158013544018</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.769230769230</v>
+        <v>-30.175438596491</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.758639605046</v>
+        <v>-79.367547952306</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,25 +1189,25 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
         <v>-25</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-57.894736842105</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="I23" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J23" s="14">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K23" s="15">
-        <v>-10.344827586206</v>
+        <v>-16.438356164383</v>
       </c>
       <c r="L23" s="15">
-        <v>-40.229885057471</v>
+        <v>-35.789473684210</v>
       </c>
       <c r="M23" s="15">
-        <v>-1.886792452830</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.689655172413</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F24" s="14">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G24" s="14">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.666666666666</v>
+        <v>-23.703703703703</v>
       </c>
       <c r="I24" s="14">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="J24" s="14">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.090090090090</v>
+        <v>-16.804979253112</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.985037406483</v>
+        <v>-4.066985645933</v>
       </c>
       <c r="M24" s="15">
-        <v>38.602941176470</v>
+        <v>36.860068259385</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.634920634920</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J25" s="14">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.582278481012</v>
+        <v>-28.458498023715</v>
       </c>
       <c r="L25" s="15">
-        <v>10.126582278481</v>
+        <v>8.383233532934</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>15</v>
+      </c>
+      <c r="D26" s="14">
         <v>10</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>15.909090909090</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J26" s="14">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.630434782608</v>
+        <v>0.515463917525</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.218009478673</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="M26" s="15">
-        <v>-27.309236947791</v>
+        <v>-28.044280442804</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
         <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>31.25</v>
+        <v>41.176470588235</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,19 +1488,19 @@
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L29" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.454545454545</v>
+        <v>-96.116504854368</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,19 +1529,19 @@
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>-63.636363636363</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-079pct.xlsx
+++ b/data/source/weekly/cs-en-us-079pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -870,63 +870,63 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
         <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
         <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-54.545454545454</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K16" s="15">
-        <v>5.263157894736</v>
+        <v>6.349206349206</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-9.459459459459</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.454545454545</v>
+        <v>-45.081967213114</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.963855421686</v>
+        <v>-90.563380281690</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-69.565217391304</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H17" s="15">
-        <v>-45.833333333333</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J17" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K17" s="15">
-        <v>-19.333333333333</v>
+        <v>-21.604938271604</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.123287671232</v>
+        <v>-16.993464052287</v>
       </c>
       <c r="M17" s="15">
-        <v>-14.788732394366</v>
+        <v>-15.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.119565217391</v>
+        <v>-68.010075566750</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-33.846153846153</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.565217391304</v>
+        <v>-70.344827586206</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.393939393939</v>
+        <v>-89.786223277909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>42.857142857142</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
+        <v>31</v>
+      </c>
+      <c r="G19" s="14">
         <v>29</v>
       </c>
-      <c r="G19" s="14">
-        <v>33</v>
-      </c>
       <c r="H19" s="15">
-        <v>-12.121212121212</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I19" s="14">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>7.5</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>3.2</v>
+        <v>1.503759398496</v>
       </c>
       <c r="M19" s="15">
-        <v>0.78125</v>
+        <v>-2.877697841726</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.809523809523</v>
+        <v>-49.248120300751</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,25 +1110,25 @@
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
+        <v>35</v>
+      </c>
+      <c r="J20" s="14">
         <v>34</v>
       </c>
-      <c r="J20" s="14">
-        <v>33</v>
-      </c>
       <c r="K20" s="15">
-        <v>3.030303030303</v>
+        <v>2.941176470588</v>
       </c>
       <c r="L20" s="15">
-        <v>25.925925925925</v>
+        <v>29.629629629629</v>
       </c>
       <c r="M20" s="15">
-        <v>-8.108108108108</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="N20" s="15">
         <v>-83.333333333333</v>
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.5</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
         <v>125</v>
       </c>
       <c r="H21" s="18">
-        <v>-36.8</v>
+        <v>-29.6</v>
       </c>
       <c r="I21" s="17">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="J21" s="17">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.238095238095</v>
+        <v>-6.013363028953</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.158013544018</v>
+        <v>-8.658008658008</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.175438596491</v>
+        <v>-30.819672131147</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.367547952306</v>
+        <v>-79.434697855750</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-53.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H23" s="15">
-        <v>-54.838709677419</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.438356164383</v>
+        <v>-14.102564102564</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.789473684210</v>
+        <v>-31.632653061224</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>1.515151515151</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.842105263157</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F24" s="14">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.703703703703</v>
+        <v>-28.676470588235</v>
       </c>
       <c r="I24" s="14">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J24" s="14">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.804979253112</v>
+        <v>-16.374269005848</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.066985645933</v>
+        <v>-3.160270880361</v>
       </c>
       <c r="M24" s="15">
-        <v>36.860068259385</v>
+        <v>36.190476190476</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
         <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I25" s="14">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="J25" s="14">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.458498023715</v>
+        <v>-29.588014981273</v>
       </c>
       <c r="L25" s="15">
-        <v>8.383233532934</v>
+        <v>6.214689265536</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
         <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>38.461538461538</v>
+        <v>32.558139534883</v>
       </c>
       <c r="I26" s="14">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="J26" s="14">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="K26" s="15">
-        <v>0.515463917525</v>
+        <v>2.450980392156</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.958904109589</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.044280442804</v>
+        <v>-29.865771812080</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
         <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>12</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L28" s="15">
-        <v>41.176470588235</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1494,13 +1494,13 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>-80.952380952380</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.116504854368</v>
+        <v>-96.330275229357</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-73.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
+        <v>50</v>
+      </c>
+      <c r="L31" s="15">
         <v>100</v>
-      </c>
-      <c r="L31" s="15">
-        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
